--- a/Horarios/Colectivos/322-Canuelas/LaboralMarcosPaz.xlsx
+++ b/Horarios/Colectivos/322-Canuelas/LaboralMarcosPaz.xlsx
@@ -158,7 +158,7 @@
     <tableColumn id="1" name="Tipo"/>
     <tableColumn id="2" name="Formacion"/>
     <tableColumn id="3" name="Cañuelas"/>
-    <tableColumn id="4" name="Las Heras"/>
+    <tableColumn id="4" name="General Las Heras"/>
     <tableColumn id="5" name="Marcos Paz"/>
   </tableColumns>
 </table>
@@ -481,7 +481,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Las Heras</t>
+          <t>General Las Heras</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -498,17 +498,19 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>135_104008-1</t>
+          <t>322 E · 04:20</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.2916666666666667</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.1805555555555556</v>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3631944444444444</v>
+        <v>0.2611111111111111</v>
       </c>
     </row>
     <row r="3">
@@ -519,17 +521,19 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>135_104009-1</t>
+          <t>322 D · 06:13</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.5076388888888889</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.5298611111111111</v>
+        <v>0.3118055555555556</v>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -540,17 +544,19 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>135_104010-1</t>
+          <t>322 E · 12:20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.6743055555555556</v>
+        <v>0.5138888888888888</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.6965277777777777</v>
+        <v>0.5944444444444444</v>
       </c>
     </row>
     <row r="5">
@@ -559,10 +565,22 @@
           <t>Empresa</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>322 D · 14:13</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.5923611111111111</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.6479166666666667</v>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -570,10 +588,22 @@
           <t>LIBERTADOR SAN MARTIN SAT</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>322 D · 16:33</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.6895833333333333</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -581,10 +611,22 @@
           <t>Recorrido</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n"/>
-      <c r="C7" s="1" t="n"/>
-      <c r="D7" s="1" t="n"/>
-      <c r="E7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>322 D · 18:53</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0.7868055555555555</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.8451388888888889</v>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -674,7 +716,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="n"/>
@@ -694,7 +736,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46266</v>
+        <v>46276</v>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>
@@ -715,7 +757,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>https://www.argentina.gob.ar/sube/cuandosubo</t>
+          <t>https://moovitapp.com/index/es-419/transporte_p%C3%BAblico-line-322-Buenos_Aires-1602-855399-579299-10</t>
         </is>
       </c>
       <c r="B20" s="1" t="n"/>
@@ -737,7 +779,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>https://cuandosubo.sube.gob.ar/onebusaway-api-webapp/api/where</t>
+          <t>https://moovitapp.com/index/es-419/transporte_p%C3%BAblico-time-322-Buenos_Aires-1602-855399-579299-6997976-0</t>
         </is>
       </c>
       <c r="B22" s="1" t="n"/>
@@ -759,7 +801,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Estimado</t>
         </is>
       </c>
       <c r="B24" s="1" t="n"/>
